--- a/Data/Building/Lab.AC001.xlsx
+++ b/Data/Building/Lab.AC001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709853897</v>
+        <v>1712535102</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709870223</v>
+        <v>1712554880</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1710636792</v>
+        <v>1712794794</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1710656350</v>
+        <v>1712811390</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1710721130</v>
+        <v>1714088687</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1710738289</v>
+        <v>1714102852</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +695,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
